--- a/artfynd/A 28288-2024 artfynd.xlsx
+++ b/artfynd/A 28288-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120288877</v>
+        <v>120288878</v>
       </c>
       <c r="B2" t="n">
-        <v>92030</v>
+        <v>89650</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120288900</v>
+        <v>120288724</v>
       </c>
       <c r="B3" t="n">
-        <v>90488</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,30 +793,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3242</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489091</v>
+        <v>488990</v>
       </c>
       <c r="R3" t="n">
-        <v>6900147</v>
+        <v>6900127</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120288767</v>
+        <v>120288874</v>
       </c>
       <c r="B4" t="n">
-        <v>79115</v>
+        <v>91874</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489029</v>
+        <v>489093</v>
       </c>
       <c r="R4" t="n">
-        <v>6900127</v>
+        <v>6900133</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120288878</v>
+        <v>120288895</v>
       </c>
       <c r="B5" t="n">
-        <v>89633</v>
+        <v>77474</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1010,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1962</v>
+        <v>6487</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489093</v>
+        <v>489091</v>
       </c>
       <c r="R5" t="n">
-        <v>6900133</v>
+        <v>6900147</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120288874</v>
+        <v>120288900</v>
       </c>
       <c r="B6" t="n">
-        <v>91856</v>
+        <v>90506</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1116,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2059</v>
+        <v>3242</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489093</v>
+        <v>489091</v>
       </c>
       <c r="R6" t="n">
-        <v>6900133</v>
+        <v>6900147</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1205,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120288719</v>
+        <v>120288863</v>
       </c>
       <c r="B7" t="n">
-        <v>78262</v>
+        <v>92048</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1222,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488968</v>
+        <v>489093</v>
       </c>
       <c r="R7" t="n">
-        <v>6900135</v>
+        <v>6900121</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1311,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120288895</v>
+        <v>120288877</v>
       </c>
       <c r="B8" t="n">
-        <v>77458</v>
+        <v>92048</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6487</v>
+        <v>2079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489091</v>
+        <v>489093</v>
       </c>
       <c r="R8" t="n">
-        <v>6900147</v>
+        <v>6900133</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1417,10 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120288759</v>
+        <v>120288767</v>
       </c>
       <c r="B9" t="n">
-        <v>91844</v>
+        <v>79131</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1430,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4365</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1523,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120288897</v>
+        <v>120288719</v>
       </c>
       <c r="B10" t="n">
-        <v>79144</v>
+        <v>78278</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1540,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489091</v>
+        <v>488968</v>
       </c>
       <c r="R10" t="n">
-        <v>6900147</v>
+        <v>6900135</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1629,10 +1630,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120288863</v>
+        <v>120288765</v>
       </c>
       <c r="B11" t="n">
-        <v>92030</v>
+        <v>78278</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1646,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1672,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489093</v>
+        <v>489029</v>
       </c>
       <c r="R11" t="n">
-        <v>6900121</v>
+        <v>6900127</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1735,10 +1736,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120288765</v>
+        <v>120288867</v>
       </c>
       <c r="B12" t="n">
-        <v>78262</v>
+        <v>91874</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1752,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1778,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489029</v>
+        <v>489093</v>
       </c>
       <c r="R12" t="n">
-        <v>6900127</v>
+        <v>6900121</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1841,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120288867</v>
+        <v>120288897</v>
       </c>
       <c r="B13" t="n">
-        <v>91856</v>
+        <v>79160</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1858,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1884,10 +1885,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489093</v>
+        <v>489091</v>
       </c>
       <c r="R13" t="n">
-        <v>6900121</v>
+        <v>6900147</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1947,10 +1948,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120288724</v>
+        <v>120288759</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
+        <v>91862</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,27 +1964,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4365</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488990</v>
+        <v>489029</v>
       </c>
       <c r="R14" t="n">
         <v>6900127</v>

--- a/artfynd/A 28288-2024 artfynd.xlsx
+++ b/artfynd/A 28288-2024 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120288724</v>
+        <v>120288874</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>91874</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,31 +793,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488990</v>
+        <v>489093</v>
       </c>
       <c r="R3" t="n">
-        <v>6900127</v>
+        <v>6900133</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -888,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120288874</v>
+        <v>120288724</v>
       </c>
       <c r="B4" t="n">
-        <v>91874</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,30 +899,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2059</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489093</v>
+        <v>488990</v>
       </c>
       <c r="R4" t="n">
-        <v>6900133</v>
+        <v>6900127</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>

--- a/artfynd/A 28288-2024 artfynd.xlsx
+++ b/artfynd/A 28288-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120288878</v>
+        <v>120288900</v>
       </c>
       <c r="B2" t="n">
-        <v>89650</v>
+        <v>90506</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1962</v>
+        <v>3242</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489093</v>
+        <v>489091</v>
       </c>
       <c r="R2" t="n">
-        <v>6900133</v>
+        <v>6900147</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120288874</v>
+        <v>120288863</v>
       </c>
       <c r="B3" t="n">
-        <v>91874</v>
+        <v>92048</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>2079</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,7 +827,7 @@
         <v>489093</v>
       </c>
       <c r="R3" t="n">
-        <v>6900133</v>
+        <v>6900121</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120288724</v>
+        <v>120288759</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>91862</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,27 +903,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -931,7 +930,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488990</v>
+        <v>489029</v>
       </c>
       <c r="R4" t="n">
         <v>6900127</v>
@@ -994,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120288895</v>
+        <v>120288719</v>
       </c>
       <c r="B5" t="n">
-        <v>77474</v>
+        <v>78278</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1037,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489091</v>
+        <v>488968</v>
       </c>
       <c r="R5" t="n">
-        <v>6900147</v>
+        <v>6900135</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1100,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120288900</v>
+        <v>120288877</v>
       </c>
       <c r="B6" t="n">
-        <v>90506</v>
+        <v>92048</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3242</v>
+        <v>2079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489091</v>
+        <v>489093</v>
       </c>
       <c r="R6" t="n">
-        <v>6900147</v>
+        <v>6900133</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1206,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120288863</v>
+        <v>120288897</v>
       </c>
       <c r="B7" t="n">
-        <v>92048</v>
+        <v>79160</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1249,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489093</v>
+        <v>489091</v>
       </c>
       <c r="R7" t="n">
-        <v>6900121</v>
+        <v>6900147</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1312,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120288877</v>
+        <v>120288878</v>
       </c>
       <c r="B8" t="n">
-        <v>92048</v>
+        <v>89650</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1418,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120288767</v>
+        <v>120288874</v>
       </c>
       <c r="B9" t="n">
-        <v>79131</v>
+        <v>91874</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>2059</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1461,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>489029</v>
+        <v>489093</v>
       </c>
       <c r="R9" t="n">
-        <v>6900127</v>
+        <v>6900133</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1524,7 +1523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120288719</v>
+        <v>120288765</v>
       </c>
       <c r="B10" t="n">
         <v>78278</v>
@@ -1567,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488968</v>
+        <v>489029</v>
       </c>
       <c r="R10" t="n">
-        <v>6900135</v>
+        <v>6900127</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1630,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120288765</v>
+        <v>120288867</v>
       </c>
       <c r="B11" t="n">
-        <v>78278</v>
+        <v>91874</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489029</v>
+        <v>489093</v>
       </c>
       <c r="R11" t="n">
-        <v>6900127</v>
+        <v>6900121</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1736,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120288867</v>
+        <v>120288767</v>
       </c>
       <c r="B12" t="n">
-        <v>91874</v>
+        <v>79131</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2059</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1779,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489093</v>
+        <v>489029</v>
       </c>
       <c r="R12" t="n">
-        <v>6900121</v>
+        <v>6900127</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1842,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120288897</v>
+        <v>120288724</v>
       </c>
       <c r="B13" t="n">
-        <v>79160</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1854,30 +1853,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489091</v>
+        <v>488990</v>
       </c>
       <c r="R13" t="n">
-        <v>6900147</v>
+        <v>6900127</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120288759</v>
+        <v>120288895</v>
       </c>
       <c r="B14" t="n">
-        <v>91862</v>
+        <v>77474</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1960,25 +1960,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4365</v>
+        <v>6487</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489029</v>
+        <v>489091</v>
       </c>
       <c r="R14" t="n">
-        <v>6900127</v>
+        <v>6900147</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>

--- a/artfynd/A 28288-2024 artfynd.xlsx
+++ b/artfynd/A 28288-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120288900</v>
+        <v>120288765</v>
       </c>
       <c r="B2" t="n">
-        <v>90506</v>
+        <v>78278</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3242</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489091</v>
+        <v>489029</v>
       </c>
       <c r="R2" t="n">
-        <v>6900147</v>
+        <v>6900127</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120288863</v>
+        <v>120288900</v>
       </c>
       <c r="B3" t="n">
-        <v>92048</v>
+        <v>90506</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2079</v>
+        <v>3242</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489093</v>
+        <v>489091</v>
       </c>
       <c r="R3" t="n">
-        <v>6900121</v>
+        <v>6900147</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120288759</v>
+        <v>120288867</v>
       </c>
       <c r="B4" t="n">
-        <v>91862</v>
+        <v>91874</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4365</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489029</v>
+        <v>489093</v>
       </c>
       <c r="R4" t="n">
-        <v>6900127</v>
+        <v>6900121</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120288719</v>
+        <v>120288897</v>
       </c>
       <c r="B5" t="n">
-        <v>78278</v>
+        <v>79160</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488968</v>
+        <v>489091</v>
       </c>
       <c r="R5" t="n">
-        <v>6900135</v>
+        <v>6900147</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120288877</v>
+        <v>120288724</v>
       </c>
       <c r="B6" t="n">
-        <v>92048</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,30 +1111,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1142,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489093</v>
+        <v>488990</v>
       </c>
       <c r="R6" t="n">
-        <v>6900133</v>
+        <v>6900127</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1205,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120288897</v>
+        <v>120288863</v>
       </c>
       <c r="B7" t="n">
-        <v>79160</v>
+        <v>92048</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1222,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489091</v>
+        <v>489093</v>
       </c>
       <c r="R7" t="n">
-        <v>6900147</v>
+        <v>6900121</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1417,10 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120288874</v>
+        <v>120288719</v>
       </c>
       <c r="B9" t="n">
-        <v>91874</v>
+        <v>78278</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1434,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2059</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1460,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>489093</v>
+        <v>488968</v>
       </c>
       <c r="R9" t="n">
-        <v>6900133</v>
+        <v>6900135</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1523,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120288765</v>
+        <v>120288874</v>
       </c>
       <c r="B10" t="n">
-        <v>78278</v>
+        <v>91874</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1540,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489029</v>
+        <v>489093</v>
       </c>
       <c r="R10" t="n">
-        <v>6900127</v>
+        <v>6900133</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1629,10 +1630,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120288867</v>
+        <v>120288895</v>
       </c>
       <c r="B11" t="n">
-        <v>91874</v>
+        <v>77474</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1646,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2059</v>
+        <v>6487</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1672,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489093</v>
+        <v>489091</v>
       </c>
       <c r="R11" t="n">
-        <v>6900121</v>
+        <v>6900147</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1841,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120288724</v>
+        <v>120288759</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
+        <v>91862</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,27 +1858,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>4365</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488990</v>
+        <v>489029</v>
       </c>
       <c r="R13" t="n">
         <v>6900127</v>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120288895</v>
+        <v>120288877</v>
       </c>
       <c r="B14" t="n">
-        <v>77474</v>
+        <v>92048</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1964,21 +1964,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6487</v>
+        <v>2079</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489091</v>
+        <v>489093</v>
       </c>
       <c r="R14" t="n">
-        <v>6900147</v>
+        <v>6900133</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>

--- a/artfynd/A 28288-2024 artfynd.xlsx
+++ b/artfynd/A 28288-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120288765</v>
+        <v>120288719</v>
       </c>
       <c r="B2" t="n">
         <v>78278</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489029</v>
+        <v>488968</v>
       </c>
       <c r="R2" t="n">
-        <v>6900127</v>
+        <v>6900135</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120288900</v>
+        <v>120288897</v>
       </c>
       <c r="B3" t="n">
-        <v>90506</v>
+        <v>79160</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3242</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120288867</v>
+        <v>120288767</v>
       </c>
       <c r="B4" t="n">
-        <v>91874</v>
+        <v>79131</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2059</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489093</v>
+        <v>489029</v>
       </c>
       <c r="R4" t="n">
-        <v>6900121</v>
+        <v>6900127</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120288897</v>
+        <v>120288878</v>
       </c>
       <c r="B5" t="n">
-        <v>79160</v>
+        <v>89650</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489091</v>
+        <v>489093</v>
       </c>
       <c r="R5" t="n">
-        <v>6900147</v>
+        <v>6900133</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120288724</v>
+        <v>120288877</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>92048</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,31 +1111,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1143,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488990</v>
+        <v>489093</v>
       </c>
       <c r="R6" t="n">
-        <v>6900127</v>
+        <v>6900133</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1206,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120288863</v>
+        <v>120288765</v>
       </c>
       <c r="B7" t="n">
-        <v>92048</v>
+        <v>78278</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1249,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489093</v>
+        <v>489029</v>
       </c>
       <c r="R7" t="n">
-        <v>6900121</v>
+        <v>6900127</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1312,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120288878</v>
+        <v>120288900</v>
       </c>
       <c r="B8" t="n">
-        <v>89650</v>
+        <v>90506</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1962</v>
+        <v>3242</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489093</v>
+        <v>489091</v>
       </c>
       <c r="R8" t="n">
-        <v>6900133</v>
+        <v>6900147</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1418,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120288719</v>
+        <v>120288867</v>
       </c>
       <c r="B9" t="n">
-        <v>78278</v>
+        <v>91874</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1461,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488968</v>
+        <v>489093</v>
       </c>
       <c r="R9" t="n">
-        <v>6900135</v>
+        <v>6900121</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1630,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120288895</v>
+        <v>120288724</v>
       </c>
       <c r="B11" t="n">
-        <v>77474</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1642,30 +1641,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489091</v>
+        <v>488990</v>
       </c>
       <c r="R11" t="n">
-        <v>6900147</v>
+        <v>6900127</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1736,10 +1736,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120288767</v>
+        <v>120288863</v>
       </c>
       <c r="B12" t="n">
-        <v>79131</v>
+        <v>92048</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,21 +1752,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>2079</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489029</v>
+        <v>489093</v>
       </c>
       <c r="R12" t="n">
-        <v>6900127</v>
+        <v>6900121</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120288877</v>
+        <v>120288895</v>
       </c>
       <c r="B14" t="n">
-        <v>92048</v>
+        <v>77474</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1964,21 +1964,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2079</v>
+        <v>6487</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489093</v>
+        <v>489091</v>
       </c>
       <c r="R14" t="n">
-        <v>6900133</v>
+        <v>6900147</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>

--- a/artfynd/A 28288-2024 artfynd.xlsx
+++ b/artfynd/A 28288-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120288719</v>
+        <v>120288724</v>
       </c>
       <c r="B2" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488968</v>
+        <v>488990</v>
       </c>
       <c r="R2" t="n">
-        <v>6900135</v>
+        <v>6900127</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120288897</v>
+        <v>120288767</v>
       </c>
       <c r="B3" t="n">
-        <v>79160</v>
+        <v>79131</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489091</v>
+        <v>489029</v>
       </c>
       <c r="R3" t="n">
-        <v>6900147</v>
+        <v>6900127</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120288767</v>
+        <v>120288867</v>
       </c>
       <c r="B4" t="n">
-        <v>79131</v>
+        <v>91874</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489029</v>
+        <v>489093</v>
       </c>
       <c r="R4" t="n">
-        <v>6900127</v>
+        <v>6900121</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120288878</v>
+        <v>120288900</v>
       </c>
       <c r="B5" t="n">
-        <v>89650</v>
+        <v>90506</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1010,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1962</v>
+        <v>3242</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489093</v>
+        <v>489091</v>
       </c>
       <c r="R5" t="n">
-        <v>6900133</v>
+        <v>6900147</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120288877</v>
+        <v>120288719</v>
       </c>
       <c r="B6" t="n">
-        <v>92048</v>
+        <v>78278</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1116,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489093</v>
+        <v>488968</v>
       </c>
       <c r="R6" t="n">
-        <v>6900133</v>
+        <v>6900135</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1205,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120288765</v>
+        <v>120288877</v>
       </c>
       <c r="B7" t="n">
-        <v>78278</v>
+        <v>92048</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1222,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489029</v>
+        <v>489093</v>
       </c>
       <c r="R7" t="n">
-        <v>6900127</v>
+        <v>6900133</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1311,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120288900</v>
+        <v>120288897</v>
       </c>
       <c r="B8" t="n">
-        <v>90506</v>
+        <v>79160</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3242</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,10 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120288867</v>
+        <v>120288878</v>
       </c>
       <c r="B9" t="n">
-        <v>91874</v>
+        <v>89650</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1434,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1463,7 +1464,7 @@
         <v>489093</v>
       </c>
       <c r="R9" t="n">
-        <v>6900121</v>
+        <v>6900133</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1523,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120288874</v>
+        <v>120288863</v>
       </c>
       <c r="B10" t="n">
-        <v>91874</v>
+        <v>92048</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1540,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2059</v>
+        <v>2079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1569,7 +1570,7 @@
         <v>489093</v>
       </c>
       <c r="R10" t="n">
-        <v>6900133</v>
+        <v>6900121</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1629,10 +1630,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120288724</v>
+        <v>120288895</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
+        <v>77474</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,31 +1642,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488990</v>
+        <v>489091</v>
       </c>
       <c r="R11" t="n">
-        <v>6900127</v>
+        <v>6900147</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1736,10 +1736,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120288863</v>
+        <v>120288874</v>
       </c>
       <c r="B12" t="n">
-        <v>92048</v>
+        <v>91874</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,21 +1752,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2079</v>
+        <v>2059</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1782,7 +1782,7 @@
         <v>489093</v>
       </c>
       <c r="R12" t="n">
-        <v>6900121</v>
+        <v>6900133</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1842,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120288759</v>
+        <v>120288765</v>
       </c>
       <c r="B13" t="n">
-        <v>91862</v>
+        <v>78278</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1854,25 +1854,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4365</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120288895</v>
+        <v>120288759</v>
       </c>
       <c r="B14" t="n">
-        <v>77474</v>
+        <v>91862</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1960,25 +1960,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6487</v>
+        <v>4365</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489091</v>
+        <v>489029</v>
       </c>
       <c r="R14" t="n">
-        <v>6900147</v>
+        <v>6900127</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>

--- a/artfynd/A 28288-2024 artfynd.xlsx
+++ b/artfynd/A 28288-2024 artfynd.xlsx
@@ -1842,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120288765</v>
+        <v>120288759</v>
       </c>
       <c r="B13" t="n">
-        <v>78278</v>
+        <v>91862</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1854,25 +1854,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>4365</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120288759</v>
+        <v>120288765</v>
       </c>
       <c r="B14" t="n">
-        <v>91862</v>
+        <v>78278</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1960,25 +1960,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4365</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>

--- a/artfynd/A 28288-2024 artfynd.xlsx
+++ b/artfynd/A 28288-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120288767</v>
+        <v>120288877</v>
       </c>
       <c r="B3" t="n">
-        <v>79131</v>
+        <v>92048</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>2079</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489029</v>
+        <v>489093</v>
       </c>
       <c r="R3" t="n">
-        <v>6900127</v>
+        <v>6900133</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120288867</v>
+        <v>120288897</v>
       </c>
       <c r="B4" t="n">
-        <v>91874</v>
+        <v>79160</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489093</v>
+        <v>489091</v>
       </c>
       <c r="R4" t="n">
-        <v>6900121</v>
+        <v>6900147</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -994,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120288900</v>
+        <v>120288867</v>
       </c>
       <c r="B5" t="n">
-        <v>90506</v>
+        <v>91874</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,21 +1010,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3242</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489091</v>
+        <v>489093</v>
       </c>
       <c r="R5" t="n">
-        <v>6900147</v>
+        <v>6900121</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120288719</v>
+        <v>120288900</v>
       </c>
       <c r="B6" t="n">
-        <v>78278</v>
+        <v>90506</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,21 +1116,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>3242</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488968</v>
+        <v>489091</v>
       </c>
       <c r="R6" t="n">
-        <v>6900135</v>
+        <v>6900147</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1206,7 +1206,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120288877</v>
+        <v>120288863</v>
       </c>
       <c r="B7" t="n">
         <v>92048</v>
@@ -1252,7 +1252,7 @@
         <v>489093</v>
       </c>
       <c r="R7" t="n">
-        <v>6900133</v>
+        <v>6900121</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120288897</v>
+        <v>120288765</v>
       </c>
       <c r="B8" t="n">
-        <v>79160</v>
+        <v>78278</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489091</v>
+        <v>489029</v>
       </c>
       <c r="R8" t="n">
-        <v>6900147</v>
+        <v>6900127</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1524,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120288863</v>
+        <v>120288767</v>
       </c>
       <c r="B10" t="n">
-        <v>92048</v>
+        <v>79131</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,21 +1540,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2079</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489093</v>
+        <v>489029</v>
       </c>
       <c r="R10" t="n">
-        <v>6900121</v>
+        <v>6900127</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1630,10 +1630,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120288895</v>
+        <v>120288719</v>
       </c>
       <c r="B11" t="n">
-        <v>77474</v>
+        <v>78278</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,21 +1646,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489091</v>
+        <v>488968</v>
       </c>
       <c r="R11" t="n">
-        <v>6900147</v>
+        <v>6900135</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1736,10 +1736,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120288874</v>
+        <v>120288895</v>
       </c>
       <c r="B12" t="n">
-        <v>91874</v>
+        <v>77474</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,21 +1752,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2059</v>
+        <v>6487</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489093</v>
+        <v>489091</v>
       </c>
       <c r="R12" t="n">
-        <v>6900133</v>
+        <v>6900147</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120288765</v>
+        <v>120288874</v>
       </c>
       <c r="B14" t="n">
-        <v>78278</v>
+        <v>91874</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1964,21 +1964,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489029</v>
+        <v>489093</v>
       </c>
       <c r="R14" t="n">
-        <v>6900127</v>
+        <v>6900133</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>

--- a/artfynd/A 28288-2024 artfynd.xlsx
+++ b/artfynd/A 28288-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120288724</v>
+        <v>120288895</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>77474</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488990</v>
+        <v>489091</v>
       </c>
       <c r="R2" t="n">
-        <v>6900127</v>
+        <v>6900147</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -782,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120288877</v>
+        <v>120288724</v>
       </c>
       <c r="B3" t="n">
-        <v>92048</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,30 +793,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489093</v>
+        <v>488990</v>
       </c>
       <c r="R3" t="n">
-        <v>6900133</v>
+        <v>6900127</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120288897</v>
+        <v>120288863</v>
       </c>
       <c r="B4" t="n">
-        <v>79160</v>
+        <v>92048</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489091</v>
+        <v>489093</v>
       </c>
       <c r="R4" t="n">
-        <v>6900147</v>
+        <v>6900121</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120288900</v>
+        <v>120288767</v>
       </c>
       <c r="B6" t="n">
-        <v>90506</v>
+        <v>79131</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,21 +1116,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3242</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489091</v>
+        <v>489029</v>
       </c>
       <c r="R6" t="n">
-        <v>6900147</v>
+        <v>6900127</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120288863</v>
+        <v>120288897</v>
       </c>
       <c r="B7" t="n">
-        <v>92048</v>
+        <v>79160</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,21 +1222,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489093</v>
+        <v>489091</v>
       </c>
       <c r="R7" t="n">
-        <v>6900121</v>
+        <v>6900147</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120288765</v>
+        <v>120288878</v>
       </c>
       <c r="B8" t="n">
-        <v>78278</v>
+        <v>89650</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489029</v>
+        <v>489093</v>
       </c>
       <c r="R8" t="n">
-        <v>6900127</v>
+        <v>6900133</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1418,10 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120288878</v>
+        <v>120288765</v>
       </c>
       <c r="B9" t="n">
-        <v>89650</v>
+        <v>78278</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,21 +1434,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>489093</v>
+        <v>489029</v>
       </c>
       <c r="R9" t="n">
-        <v>6900133</v>
+        <v>6900127</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1524,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120288767</v>
+        <v>120288877</v>
       </c>
       <c r="B10" t="n">
-        <v>79131</v>
+        <v>92048</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,21 +1540,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>2079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489029</v>
+        <v>489093</v>
       </c>
       <c r="R10" t="n">
-        <v>6900127</v>
+        <v>6900133</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1630,10 +1630,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120288719</v>
+        <v>120288900</v>
       </c>
       <c r="B11" t="n">
-        <v>78278</v>
+        <v>90506</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,21 +1646,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>3242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488968</v>
+        <v>489091</v>
       </c>
       <c r="R11" t="n">
-        <v>6900135</v>
+        <v>6900147</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1736,10 +1736,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120288895</v>
+        <v>120288719</v>
       </c>
       <c r="B12" t="n">
-        <v>77474</v>
+        <v>78278</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,21 +1752,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489091</v>
+        <v>488968</v>
       </c>
       <c r="R12" t="n">
-        <v>6900147</v>
+        <v>6900135</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1842,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120288759</v>
+        <v>120288874</v>
       </c>
       <c r="B13" t="n">
-        <v>91862</v>
+        <v>91874</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1854,25 +1854,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4365</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489029</v>
+        <v>489093</v>
       </c>
       <c r="R13" t="n">
-        <v>6900127</v>
+        <v>6900133</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120288874</v>
+        <v>120288759</v>
       </c>
       <c r="B14" t="n">
-        <v>91874</v>
+        <v>91862</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1960,25 +1960,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2059</v>
+        <v>4365</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489093</v>
+        <v>489029</v>
       </c>
       <c r="R14" t="n">
-        <v>6900133</v>
+        <v>6900127</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>

--- a/artfynd/A 28288-2024 artfynd.xlsx
+++ b/artfynd/A 28288-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120288874</v>
+        <v>120302097</v>
       </c>
       <c r="B2" t="n">
-        <v>91924</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489093</v>
+        <v>489105</v>
       </c>
       <c r="R2" t="n">
-        <v>6900133</v>
+        <v>6900160</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120288900</v>
+        <v>120288878</v>
       </c>
       <c r="B3" t="n">
-        <v>90558</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3242</v>
+        <v>1962</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489091</v>
+        <v>489093</v>
       </c>
       <c r="R3" t="n">
-        <v>6900147</v>
+        <v>6900133</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120288878</v>
+        <v>120288867</v>
       </c>
       <c r="B4" t="n">
-        <v>89692</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1962</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,7 +918,7 @@
         <v>489093</v>
       </c>
       <c r="R4" t="n">
-        <v>6900133</v>
+        <v>6900121</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120288895</v>
+        <v>120288874</v>
       </c>
       <c r="B5" t="n">
-        <v>77493</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6487</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489091</v>
+        <v>489093</v>
       </c>
       <c r="R5" t="n">
-        <v>6900147</v>
+        <v>6900133</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,19 +1079,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120288867</v>
+        <v>120302102</v>
       </c>
       <c r="B6" t="n">
-        <v>91924</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1142,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489093</v>
+        <v>489105</v>
       </c>
       <c r="R6" t="n">
-        <v>6900121</v>
+        <v>6900160</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1205,43 +1180,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120288724</v>
+        <v>120288863</v>
       </c>
       <c r="B7" t="n">
-        <v>98001</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1249,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488990</v>
+        <v>489093</v>
       </c>
       <c r="R7" t="n">
-        <v>6900127</v>
+        <v>6900121</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1315,12 +1284,7 @@
         <v>120288877</v>
       </c>
       <c r="B8" t="n">
-        <v>92104</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,15 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120288863</v>
+        <v>120288900</v>
       </c>
       <c r="B9" t="n">
-        <v>92104</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1434,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2079</v>
+        <v>3242</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1461,10 +1420,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>489093</v>
+        <v>489091</v>
       </c>
       <c r="R9" t="n">
-        <v>6900121</v>
+        <v>6900147</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1524,15 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120288767</v>
+        <v>120288735</v>
       </c>
       <c r="B10" t="n">
-        <v>79150</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1540,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1567,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489029</v>
+        <v>488984</v>
       </c>
       <c r="R10" t="n">
-        <v>6900127</v>
+        <v>6900157</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1630,15 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120288719</v>
+        <v>120288743</v>
       </c>
       <c r="B11" t="n">
-        <v>78297</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1646,21 +1595,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1622,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488968</v>
+        <v>488997</v>
       </c>
       <c r="R11" t="n">
-        <v>6900135</v>
+        <v>6900148</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1736,37 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120288765</v>
+        <v>120288759</v>
       </c>
       <c r="B12" t="n">
-        <v>78297</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>4365</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1842,15 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120288759</v>
+        <v>120288907</v>
       </c>
       <c r="B13" t="n">
-        <v>91912</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1858,21 +1797,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1885,10 +1824,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489029</v>
+        <v>489067</v>
       </c>
       <c r="R13" t="n">
-        <v>6900127</v>
+        <v>6900156</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1948,37 +1887,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120288897</v>
+        <v>120302105</v>
       </c>
       <c r="B14" t="n">
-        <v>79179</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1991,10 +1925,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489091</v>
+        <v>489105</v>
       </c>
       <c r="R14" t="n">
-        <v>6900147</v>
+        <v>6900160</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2051,6 +1985,1118 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120288719</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bäckrönningen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>488968</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6900135</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Överhogdal</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120288765</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bäckrönningen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>489029</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6900127</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Överhogdal</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120288897</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bäckrönningen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>489091</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6900147</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Överhogdal</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120302100</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bäckrönningen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>489105</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6900160</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Överhogdal</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120302099</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bäckrönningen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>489105</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6900160</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Överhogdal</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120288895</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78334</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Bäckrönningen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>489091</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6900147</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Överhogdal</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120288724</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Bäckrönningen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>488990</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6900127</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Överhogdal</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120302108</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78339</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Bäckrönningen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>489105</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6900160</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Överhogdal</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120302103</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Bäckrönningen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>489105</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6900160</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Överhogdal</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120288740</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Bäckrönningen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>488984</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6900157</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Överhogdal</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120288767</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Bäckrönningen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>489029</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6900127</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Överhogdal</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28288-2024 artfynd.xlsx
+++ b/artfynd/A 28288-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120302097</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120288878</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120288867</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120288874</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120302102</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120288863</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120288877</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120288900</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120288735</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120288743</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120288759</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120288907</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120302105</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2086,6 +2156,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120288719</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2187,6 +2262,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120288765</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2288,6 +2368,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120288897</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2389,6 +2474,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120302100</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2490,6 +2580,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120302099</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2591,6 +2686,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120288895</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2693,6 +2793,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120288724</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2794,6 +2899,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120302108</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2895,6 +3005,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120302103</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2996,6 +3111,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120288740</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3097,8 +3217,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120288767</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>